--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -230,7 +230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="10.921875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.13"/>
@@ -1028,6 +1028,25 @@
         <v>0.599999999999994</v>
       </c>
     </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>45550</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <f aca="false">B43-B42</f>
+        <v>0.0199999999999996</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <f aca="false">C43-C42</f>
+        <v>0.280000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -230,7 +230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="10.921875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.13"/>
@@ -1047,6 +1047,25 @@
         <v>0.280000000000001</v>
       </c>
     </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>45557</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>89.81</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <f aca="false">B44-B43</f>
+        <v>0.0500000000000007</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <f aca="false">C44-C43</f>
+        <v>-0.569999999999993</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -230,7 +230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultColWidth="10.921875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.13"/>
@@ -1066,6 +1066,44 @@
         <v>-0.569999999999993</v>
       </c>
     </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>45564</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <f aca="false">B45-B44</f>
+        <v>0.0399999999999991</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <f aca="false">C45-C44</f>
+        <v>0.920000000000002</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="n">
+        <v>45571</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <f aca="false">B46-B45</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <f aca="false">C46-C45</f>
+        <v>-0.280000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -230,7 +230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="10.921875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.13"/>
@@ -1104,6 +1104,25 @@
         <v>-0.280000000000001</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="n">
+        <v>45578</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <f aca="false">B47-B46</f>
+        <v>-0.0599999999999987</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <f aca="false">C47-C46</f>
+        <v>0.239999999999995</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -108,7 +108,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -144,6 +144,13 @@
       <name val="Calibri"/>
       <family val="1"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,7 +195,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -213,6 +220,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -222,6 +233,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -230,7 +301,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="10.921875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.13"/>
@@ -1123,6 +1194,25 @@
         <v>0.239999999999995</v>
       </c>
     </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>45585</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <f aca="false">B48-B47</f>
+        <v>0.0199999999999996</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <f aca="false">C48-C47</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -108,7 +108,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -144,13 +144,6 @@
       <name val="Calibri"/>
       <family val="1"/>
       <charset val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC9211E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -220,7 +213,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -233,66 +226,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFC9211E"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1202,7 +1135,7 @@
         <v>30.04</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>90.69</v>
+        <v>90.25</v>
       </c>
       <c r="D48" s="1" t="n">
         <f aca="false">B48-B47</f>
@@ -1210,7 +1143,7 @@
       </c>
       <c r="E48" s="1" t="n">
         <f aca="false">C48-C47</f>
-        <v>0</v>
+        <v>-0.439999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D727FFA-CD42-47C1-AA01-4E5F00AB17E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677FC651-BC2B-44AC-B916-F646F6EA91C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="13152" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ53"/>
+  <dimension ref="A1:AMJ54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="4" customWidth="1"/>
@@ -1481,12 +1481,31 @@
         <v>90.58</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" ref="D53" si="4">B53-B52</f>
+        <f t="shared" ref="D53:D54" si="4">B53-B52</f>
         <v>9.9999999999980105E-3</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" ref="E53" si="5">C53-C52</f>
+        <f t="shared" ref="E53:E54" si="5">C53-C52</f>
         <v>-0.21999999999999886</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="4">
+        <v>45627</v>
+      </c>
+      <c r="B54" s="1">
+        <v>30.04</v>
+      </c>
+      <c r="C54" s="1">
+        <v>90.94</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" si="5"/>
+        <v>0.35999999999999943</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677FC651-BC2B-44AC-B916-F646F6EA91C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50708DD5-7E7C-4416-9827-BA50DF399A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="13152" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -479,18 +479,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:AMJ55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.89453125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="20.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" style="1" customWidth="1"/>
-    <col min="7" max="1024" width="10.90625" style="1"/>
+    <col min="1" max="1" width="12.1015625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.89453125" style="1"/>
+    <col min="3" max="3" width="12.62890625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.62890625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7890625" style="1" customWidth="1"/>
+    <col min="7" max="1024" width="10.89453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="29">
+    <row r="1" spans="1:6" ht="29.1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1481,11 +1481,11 @@
         <v>90.58</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" ref="D53:D54" si="4">B53-B52</f>
+        <f t="shared" ref="D53:D55" si="4">B53-B52</f>
         <v>9.9999999999980105E-3</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" ref="E53:E54" si="5">C53-C52</f>
+        <f t="shared" ref="E53:E55" si="5">C53-C52</f>
         <v>-0.21999999999999886</v>
       </c>
     </row>
@@ -1506,6 +1506,25 @@
       <c r="E54" s="1">
         <f t="shared" si="5"/>
         <v>0.35999999999999943</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="4">
+        <v>45634</v>
+      </c>
+      <c r="B55" s="1">
+        <v>30.04</v>
+      </c>
+      <c r="C55" s="1">
+        <v>90.93</v>
+      </c>
+      <c r="D55" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <f t="shared" si="5"/>
+        <v>-9.9999999999909051E-3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50708DD5-7E7C-4416-9827-BA50DF399A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30418BF7-A428-4D86-B329-D5A925C2102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15740" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -108,7 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -129,6 +129,19 @@
       <name val="Calibri"/>
       <family val="1"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -151,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +176,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -183,7 +205,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -479,18 +501,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.89453125" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AMJ59"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.1015625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="10.89453125" style="1"/>
-    <col min="3" max="3" width="12.62890625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="20.62890625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7890625" style="1" customWidth="1"/>
-    <col min="7" max="1024" width="10.89453125" style="1"/>
+    <col min="1" max="1" width="12.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="1" customWidth="1"/>
+    <col min="7" max="1024" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="29.1">
+    <row r="1" spans="1:6" ht="29">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1481,11 +1503,11 @@
         <v>90.58</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" ref="D53:D55" si="4">B53-B52</f>
+        <f t="shared" ref="D53:D56" si="4">B53-B52</f>
         <v>9.9999999999980105E-3</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" ref="E53:E55" si="5">C53-C52</f>
+        <f t="shared" ref="E53:E56" si="5">C53-C52</f>
         <v>-0.21999999999999886</v>
       </c>
     </row>
@@ -1509,26 +1531,102 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="4">
+      <c r="A55" s="5">
         <v>45634</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="6">
         <v>30.04</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="6">
         <v>90.93</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="6">
         <f t="shared" si="5"/>
         <v>-9.9999999999909051E-3</v>
       </c>
     </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="5">
+        <v>45641</v>
+      </c>
+      <c r="B56" s="6">
+        <v>30.04</v>
+      </c>
+      <c r="C56" s="6">
+        <v>91.14</v>
+      </c>
+      <c r="D56" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" si="5"/>
+        <v>0.20999999999999375</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="5">
+        <v>45655</v>
+      </c>
+      <c r="B57" s="6">
+        <v>30.04</v>
+      </c>
+      <c r="C57" s="6">
+        <v>91.27</v>
+      </c>
+      <c r="D57" s="6">
+        <f t="shared" ref="D57:D59" si="6">B57-B56</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="6">
+        <f t="shared" ref="E57:E59" si="7">C57-C56</f>
+        <v>0.12999999999999545</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5">
+        <v>45662</v>
+      </c>
+      <c r="B58" s="6">
+        <v>30</v>
+      </c>
+      <c r="C58" s="6">
+        <v>90.97</v>
+      </c>
+      <c r="D58" s="6">
+        <f t="shared" si="6"/>
+        <v>-3.9999999999999147E-2</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" si="7"/>
+        <v>-0.29999999999999716</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="4">
+        <v>45669</v>
+      </c>
+      <c r="B59" s="1">
+        <v>30.05</v>
+      </c>
+      <c r="C59" s="1">
+        <v>91.59</v>
+      </c>
+      <c r="D59" s="7">
+        <f t="shared" si="6"/>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="E59" s="7">
+        <f t="shared" si="7"/>
+        <v>0.62000000000000455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30418BF7-A428-4D86-B329-D5A925C2102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4258E3BC-97BD-4BCC-B504-B8397D0A91AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15740" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15910" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -164,15 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -181,11 +189,20 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,1128 +518,1185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ59"/>
+  <dimension ref="A1:AMJ62"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="20.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="6"/>
+    <col min="3" max="3" width="12.6328125" style="6" customWidth="1"/>
+    <col min="4" max="5" width="20.6328125" style="6" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" style="1" customWidth="1"/>
     <col min="7" max="1024" width="10.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>45263</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
         <v>29.67</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6">
         <v>91.47</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>45270</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
         <v>29.76</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="6">
         <v>90.89</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="6">
         <f t="shared" ref="D3:D48" si="0">B3-B2</f>
         <v>8.9999999999999858E-2</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="6">
         <f t="shared" ref="E3:E48" si="1">C3-C2</f>
         <v>-0.57999999999999829</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>45277</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>29.76</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="6">
         <v>91.12</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="6">
         <f t="shared" si="1"/>
         <v>0.23000000000000398</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>45284</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
         <v>29.79</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="6">
         <v>90.74</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="6">
         <f t="shared" si="0"/>
         <v>2.9999999999997584E-2</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="6">
         <f t="shared" si="1"/>
         <v>-0.38000000000000966</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>45291</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="6">
         <v>29.76</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="6">
         <v>90.76</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="6">
         <f t="shared" si="0"/>
         <v>-2.9999999999997584E-2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="6">
         <f t="shared" si="1"/>
         <v>2.0000000000010232E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>45298</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="6">
         <v>29.8</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
         <v>91.12</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="6">
         <f t="shared" si="1"/>
         <v>0.35999999999999943</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>45305</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="6">
         <v>29.73</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>91.75</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="6">
         <f t="shared" si="0"/>
         <v>-7.0000000000000284E-2</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="6">
         <f t="shared" si="1"/>
         <v>0.62999999999999545</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>45312</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="6">
         <v>29.72</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="6">
         <v>91.46</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="6">
         <f t="shared" si="0"/>
         <v>-1.0000000000001563E-2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="6">
         <f t="shared" si="1"/>
         <v>-0.29000000000000625</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>45319</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="6">
         <v>29.82</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="6">
         <v>91.13</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="6">
         <f t="shared" si="0"/>
         <v>0.10000000000000142</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="6">
         <f t="shared" si="1"/>
         <v>-0.32999999999999829</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>45326</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="6">
         <v>29.86</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="6">
         <v>90.75</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="6">
         <f t="shared" si="0"/>
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="6">
         <f t="shared" si="1"/>
         <v>-0.37999999999999545</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>45333</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="6">
         <v>29.87</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
         <v>90.82</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="6">
         <f t="shared" si="0"/>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="6">
         <f t="shared" si="1"/>
         <v>6.9999999999993179E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>45340</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="6">
         <v>29.8</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="6">
         <v>90.54</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="6">
         <f t="shared" si="0"/>
         <v>-7.0000000000000284E-2</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="6">
         <f t="shared" si="1"/>
         <v>-0.27999999999998693</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>45347</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="6">
         <v>29.85</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="6">
         <v>91.09</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="6">
         <f t="shared" si="1"/>
         <v>0.54999999999999716</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>45354</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <v>29.89</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="6">
         <v>90.79</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="6">
         <f t="shared" si="0"/>
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="6">
         <f t="shared" si="1"/>
         <v>-0.29999999999999716</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>45361</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>29.84</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="6">
         <v>90.76</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="6">
         <f t="shared" si="0"/>
         <v>-5.0000000000000711E-2</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="6">
         <f t="shared" si="1"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>45368</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <v>29.87</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
         <v>90.34</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="6">
         <f t="shared" si="0"/>
         <v>3.0000000000001137E-2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="6">
         <f t="shared" si="1"/>
         <v>-0.42000000000000171</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>45375</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <v>29.83</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="6">
         <v>90.65</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="6">
         <f t="shared" si="0"/>
         <v>-4.00000000000027E-2</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="6">
         <f t="shared" si="1"/>
         <v>0.31000000000000227</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>45382</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="6">
         <v>29.86</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="6">
         <v>90.5</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="6">
         <f t="shared" si="0"/>
         <v>3.0000000000001137E-2</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="6">
         <f t="shared" si="1"/>
         <v>-0.15000000000000568</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>45389</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="6">
         <v>29.91</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>89.74</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="6">
         <f t="shared" si="1"/>
         <v>-0.76000000000000512</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>45396</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="6">
         <v>29.86</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="6">
         <v>89.97</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="6">
         <f t="shared" si="0"/>
         <v>-5.0000000000000711E-2</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="6">
         <f t="shared" si="1"/>
         <v>0.23000000000000398</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>45403</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="6">
         <v>29.87</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
         <v>90.02</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="6">
         <f t="shared" si="0"/>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="6">
         <f t="shared" si="1"/>
         <v>4.9999999999997158E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>45410</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="6">
         <v>29.83</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="6">
         <v>90.67</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="6">
         <f t="shared" si="0"/>
         <v>-4.00000000000027E-2</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="6">
         <f t="shared" si="1"/>
         <v>0.65000000000000568</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>45417</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="6">
         <v>29.88</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="6">
         <v>90.17</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="6">
         <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>45424</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="6">
         <v>29.87</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="6">
         <v>89.54</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="6">
         <f t="shared" si="0"/>
         <v>-9.9999999999980105E-3</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="6">
         <f t="shared" si="1"/>
         <v>-0.62999999999999545</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>45431</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="6">
         <v>29.86</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="6">
         <v>90.19</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="6">
         <f t="shared" si="0"/>
         <v>-1.0000000000001563E-2</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="6">
         <f t="shared" si="1"/>
         <v>0.64999999999999147</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>45438</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="6">
         <v>29.87</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="6">
         <v>89.97</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="6">
         <f t="shared" si="0"/>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="6">
         <f t="shared" si="1"/>
         <v>-0.21999999999999886</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>45445</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="6">
         <v>29.89</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="6">
         <v>90.34</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="6">
         <f t="shared" si="0"/>
         <v>1.9999999999999574E-2</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="6">
         <f t="shared" si="1"/>
         <v>0.37000000000000455</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>45452</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="6">
         <v>29.89</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="6">
         <v>90.1</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="6">
         <f t="shared" si="1"/>
         <v>-0.24000000000000909</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>45459</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="6">
         <v>29.92</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="6">
         <v>90.28</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="6">
         <f t="shared" si="0"/>
         <v>3.0000000000001137E-2</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="6">
         <f t="shared" si="1"/>
         <v>0.18000000000000682</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>45466</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="6">
         <v>29.9</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="6">
         <v>89.93</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="6">
         <f t="shared" si="0"/>
         <v>-2.0000000000003126E-2</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="6">
         <f t="shared" si="1"/>
         <v>-0.34999999999999432</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>45473</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="6">
         <v>29.87</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="6">
         <v>89.87</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="6">
         <f t="shared" si="0"/>
         <v>-2.9999999999997584E-2</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="6">
         <f t="shared" si="1"/>
         <v>-6.0000000000002274E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>45480</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="6">
         <v>29.96</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="6">
         <v>90.02</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="6">
         <f t="shared" si="0"/>
         <v>8.9999999999999858E-2</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="6">
         <f t="shared" si="1"/>
         <v>0.14999999999999147</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>45487</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="6">
         <v>29.93</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="6">
         <v>89.58</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="6">
         <f t="shared" si="0"/>
         <v>-3.0000000000001137E-2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="6">
         <f t="shared" si="1"/>
         <v>-0.43999999999999773</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>45494</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="6">
         <v>29.95</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="6">
         <v>89.35</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="6">
         <f t="shared" si="0"/>
         <v>1.9999999999999574E-2</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="6">
         <f t="shared" si="1"/>
         <v>-0.23000000000000398</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>45501</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="6">
         <v>29.93</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="6">
         <v>89.5</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="6">
         <f t="shared" si="0"/>
         <v>-1.9999999999999574E-2</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="6">
         <f t="shared" si="1"/>
         <v>0.15000000000000568</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>45508</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="6">
         <v>29.93</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="6">
         <v>89.34</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="6">
         <f t="shared" si="1"/>
         <v>-0.15999999999999659</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>45515</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="6">
         <v>29.97</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="6">
         <v>89.37</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="6">
         <f t="shared" si="0"/>
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="6">
         <f t="shared" si="1"/>
         <v>3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
         <v>45522</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="6">
         <v>29.93</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="6">
         <v>89.84</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="6">
         <f t="shared" si="0"/>
         <v>-3.9999999999999147E-2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="6">
         <f t="shared" si="1"/>
         <v>0.46999999999999886</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>45529</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="6">
         <v>29.98</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="6">
         <v>89.94</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="6">
         <f t="shared" si="1"/>
         <v>9.9999999999994316E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <v>45536</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="6">
         <v>30.01</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="6">
         <v>89.5</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="6">
         <f t="shared" si="0"/>
         <v>3.0000000000001137E-2</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="6">
         <f t="shared" si="1"/>
         <v>-0.43999999999999773</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>45543</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="6">
         <v>29.97</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="6">
         <v>90.1</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="6">
         <f t="shared" si="0"/>
         <v>-4.00000000000027E-2</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="6">
         <f t="shared" si="1"/>
         <v>0.59999999999999432</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
         <v>45550</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="6">
         <v>29.99</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="6">
         <v>90.38</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="6">
         <f t="shared" si="0"/>
         <v>1.9999999999999574E-2</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="6">
         <f t="shared" si="1"/>
         <v>0.28000000000000114</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>45557</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="6">
         <v>30.04</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="6">
         <v>89.81</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="6">
         <f t="shared" si="0"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="6">
         <f t="shared" si="1"/>
         <v>-0.56999999999999318</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>45564</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="6">
         <v>30.08</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="6">
         <v>90.73</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="6">
         <f t="shared" si="0"/>
         <v>3.9999999999999147E-2</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="6">
         <f t="shared" si="1"/>
         <v>0.92000000000000171</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>45571</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="6">
         <v>30.08</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="6">
         <v>90.45</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="6">
         <f t="shared" si="1"/>
         <v>-0.28000000000000114</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
         <v>45578</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="6">
         <v>30.02</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="6">
         <v>90.69</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="6">
         <f t="shared" si="0"/>
         <v>-5.9999999999998721E-2</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="6">
         <f t="shared" si="1"/>
         <v>0.23999999999999488</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>45585</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="6">
         <v>30.04</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="6">
         <v>90.25</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="6">
         <f t="shared" si="0"/>
         <v>1.9999999999999574E-2</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="6">
         <f t="shared" si="1"/>
         <v>-0.43999999999999773</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>45592</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="6">
         <v>30.05</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="6">
         <v>90.25</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="6">
         <f t="shared" ref="D49:D52" si="2">B49-B48</f>
         <v>1.0000000000001563E-2</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="6">
         <f t="shared" ref="E49:E52" si="3">C49-C48</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>45599</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="6">
         <v>30.06</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="6">
         <v>90.6</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="6">
         <f t="shared" si="2"/>
         <v>9.9999999999980105E-3</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="6">
         <f t="shared" si="3"/>
         <v>0.34999999999999432</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>45606</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="6">
         <v>30.03</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="6">
         <v>90.67</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="6">
         <f t="shared" si="2"/>
         <v>-2.9999999999997584E-2</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="6">
         <f t="shared" si="3"/>
         <v>7.000000000000739E-2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>45613</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="6">
         <v>30.03</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="6">
         <v>90.8</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="6">
         <f t="shared" si="3"/>
         <v>0.12999999999999545</v>
       </c>
       <c r="F52"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>45620</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="6">
         <v>30.04</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="6">
         <v>90.58</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="6">
         <f t="shared" ref="D53:D56" si="4">B53-B52</f>
         <v>9.9999999999980105E-3</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="6">
         <f t="shared" ref="E53:E56" si="5">C53-C52</f>
         <v>-0.21999999999999886</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>45627</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="6">
         <v>30.04</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="6">
         <v>90.94</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="6">
         <f t="shared" si="5"/>
         <v>0.35999999999999943</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>45634</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="7">
         <v>30.04</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="7">
         <v>90.93</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="7">
         <f t="shared" si="5"/>
         <v>-9.9999999999909051E-3</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <v>45641</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="7">
         <v>30.04</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="7">
         <v>91.14</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="7">
         <f t="shared" si="5"/>
         <v>0.20999999999999375</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>45655</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="7">
         <v>30.04</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="7">
         <v>91.27</v>
       </c>
-      <c r="D57" s="6">
-        <f t="shared" ref="D57:D59" si="6">B57-B56</f>
+      <c r="D57" s="7">
+        <f t="shared" ref="D57:D60" si="6">B57-B56</f>
         <v>0</v>
       </c>
-      <c r="E57" s="6">
-        <f t="shared" ref="E57:E59" si="7">C57-C56</f>
+      <c r="E57" s="7">
+        <f t="shared" ref="E57:E60" si="7">C57-C56</f>
         <v>0.12999999999999545</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>45662</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="7">
         <v>30</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="7">
         <v>90.97</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="7">
         <f t="shared" si="6"/>
         <v>-3.9999999999999147E-2</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="7">
         <f t="shared" si="7"/>
         <v>-0.29999999999999716</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
         <v>45669</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="6">
         <v>30.05</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="6">
         <v>91.59</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="8">
         <f t="shared" si="6"/>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="8">
         <f t="shared" si="7"/>
         <v>0.62000000000000455</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="3">
+        <v>45678</v>
+      </c>
+      <c r="B60" s="6">
+        <v>30.08</v>
+      </c>
+      <c r="C60" s="6">
+        <v>91.35</v>
+      </c>
+      <c r="D60" s="6">
+        <f t="shared" si="6"/>
+        <v>2.9999999999997584E-2</v>
+      </c>
+      <c r="E60" s="6">
+        <f t="shared" si="7"/>
+        <v>-0.24000000000000909</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="3">
+        <v>45683</v>
+      </c>
+      <c r="B61" s="6">
+        <v>30.08</v>
+      </c>
+      <c r="C61" s="6">
+        <v>91.34</v>
+      </c>
+      <c r="D61" s="8">
+        <f t="shared" ref="D61:D62" si="8">B61-B60</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="8">
+        <f t="shared" ref="E61:E62" si="9">C61-C60</f>
+        <v>-9.9999999999909051E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="3">
+        <v>45690</v>
+      </c>
+      <c r="B62" s="6">
+        <v>30.05</v>
+      </c>
+      <c r="C62" s="6">
+        <v>91.24</v>
+      </c>
+      <c r="D62" s="8">
+        <f t="shared" si="8"/>
+        <v>-2.9999999999997584E-2</v>
+      </c>
+      <c r="E62" s="8">
+        <f t="shared" si="9"/>
+        <v>-0.10000000000000853</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4258E3BC-97BD-4BCC-B504-B8397D0A91AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217969A-B115-4B40-8ADD-7D8025899A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15910" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -113,6 +102,10 @@
       </rPr>
       <t>(mm)</t>
     </r>
+  </si>
+  <si>
+    <t>Mur route
+(inch)</t>
   </si>
 </sst>
 </file>
@@ -518,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ62"/>
+  <dimension ref="A1:AMJ63"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="3" customWidth="1"/>
@@ -545,7 +538,9 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3">
@@ -1697,6 +1692,28 @@
       <c r="E62" s="8">
         <f t="shared" si="9"/>
         <v>-0.10000000000000853</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="3">
+        <v>45697</v>
+      </c>
+      <c r="B63" s="6">
+        <v>30.05</v>
+      </c>
+      <c r="C63" s="6">
+        <v>91.36</v>
+      </c>
+      <c r="D63" s="8">
+        <f t="shared" ref="D63" si="10">B63-B62</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="8">
+        <f t="shared" ref="E63" si="11">C63-C62</f>
+        <v>0.12000000000000455</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0.76300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217969A-B115-4B40-8ADD-7D8025899A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8E6022-DF9F-4C50-AC98-8FE64D67E91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32070" yWindow="1620" windowWidth="16440" windowHeight="29040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -511,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ63"/>
+  <dimension ref="A1:AMJ79"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="3" customWidth="1"/>
@@ -1712,8 +1712,309 @@
         <f t="shared" ref="E63" si="11">C63-C62</f>
         <v>0.12000000000000455</v>
       </c>
-      <c r="F63" s="1">
-        <v>0.76300000000000001</v>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="3">
+        <v>45704</v>
+      </c>
+      <c r="B64" s="6">
+        <v>30.07</v>
+      </c>
+      <c r="C64" s="6">
+        <v>91.18</v>
+      </c>
+      <c r="D64" s="8">
+        <f t="shared" ref="D64:D68" si="12">B64-B63</f>
+        <v>1.9999999999999574E-2</v>
+      </c>
+      <c r="E64" s="8">
+        <f t="shared" ref="E64:E68" si="13">C64-C63</f>
+        <v>-0.17999999999999261</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3">
+        <v>45711</v>
+      </c>
+      <c r="B65" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="C65" s="6">
+        <v>90.7</v>
+      </c>
+      <c r="D65" s="8">
+        <f t="shared" si="12"/>
+        <v>3.0000000000001137E-2</v>
+      </c>
+      <c r="E65" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.48000000000000398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3">
+        <v>45718</v>
+      </c>
+      <c r="B66" s="6">
+        <v>30.14</v>
+      </c>
+      <c r="C66" s="6">
+        <v>90.78</v>
+      </c>
+      <c r="D66" s="8">
+        <f t="shared" si="12"/>
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="E66" s="8">
+        <f t="shared" si="13"/>
+        <v>7.9999999999998295E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3">
+        <v>45725</v>
+      </c>
+      <c r="B67" s="6">
+        <v>30.13</v>
+      </c>
+      <c r="C67" s="6">
+        <v>90.01</v>
+      </c>
+      <c r="D67" s="8">
+        <f t="shared" si="12"/>
+        <v>-1.0000000000001563E-2</v>
+      </c>
+      <c r="E67" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.76999999999999602</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3">
+        <v>45732</v>
+      </c>
+      <c r="B68" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="C68" s="6">
+        <v>90.66</v>
+      </c>
+      <c r="D68" s="8">
+        <f t="shared" si="12"/>
+        <v>-2.9999999999997584E-2</v>
+      </c>
+      <c r="E68" s="8">
+        <f t="shared" si="13"/>
+        <v>0.64999999999999147</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3">
+        <v>45739</v>
+      </c>
+      <c r="B69" s="6">
+        <v>30.14</v>
+      </c>
+      <c r="C69" s="6">
+        <v>90.41</v>
+      </c>
+      <c r="D69" s="8">
+        <f t="shared" ref="D69:D70" si="14">B69-B68</f>
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="E69" s="8">
+        <f t="shared" ref="E69:E70" si="15">C69-C68</f>
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3">
+        <v>45746</v>
+      </c>
+      <c r="B70" s="6">
+        <v>30.14</v>
+      </c>
+      <c r="C70" s="6">
+        <v>90.57</v>
+      </c>
+      <c r="D70" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="E70" s="8">
+        <f t="shared" si="15"/>
+        <v>0.15999999999999659</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3">
+        <v>45753</v>
+      </c>
+      <c r="B71" s="6">
+        <v>30.15</v>
+      </c>
+      <c r="C71" s="6">
+        <v>89.93</v>
+      </c>
+      <c r="D71" s="8">
+        <f t="shared" ref="D71:D76" si="16">B71-B70</f>
+        <v>9.9999999999980105E-3</v>
+      </c>
+      <c r="E71" s="8">
+        <f t="shared" ref="E71:E76" si="17">C71-C70</f>
+        <v>-0.63999999999998636</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3">
+        <v>45760</v>
+      </c>
+      <c r="B72" s="6">
+        <v>30.16</v>
+      </c>
+      <c r="C72" s="6">
+        <v>90.17</v>
+      </c>
+      <c r="D72" s="8">
+        <f t="shared" si="16"/>
+        <v>1.0000000000001563E-2</v>
+      </c>
+      <c r="E72" s="8">
+        <f t="shared" si="17"/>
+        <v>0.23999999999999488</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3">
+        <v>45767</v>
+      </c>
+      <c r="B73" s="6">
+        <v>30.14</v>
+      </c>
+      <c r="C73" s="6">
+        <v>90.27</v>
+      </c>
+      <c r="D73" s="8">
+        <f t="shared" si="16"/>
+        <v>-1.9999999999999574E-2</v>
+      </c>
+      <c r="E73" s="8">
+        <f t="shared" si="17"/>
+        <v>9.9999999999994316E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3">
+        <v>45774</v>
+      </c>
+      <c r="B74" s="6">
+        <v>30.16</v>
+      </c>
+      <c r="C74" s="6">
+        <v>90.38</v>
+      </c>
+      <c r="D74" s="8">
+        <f t="shared" si="16"/>
+        <v>1.9999999999999574E-2</v>
+      </c>
+      <c r="E74" s="8">
+        <f t="shared" si="17"/>
+        <v>0.10999999999999943</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3">
+        <v>45781</v>
+      </c>
+      <c r="B75" s="6">
+        <v>30.16</v>
+      </c>
+      <c r="C75" s="6">
+        <v>90.18</v>
+      </c>
+      <c r="D75" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E75" s="8">
+        <f t="shared" si="17"/>
+        <v>-0.19999999999998863</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3">
+        <v>45788</v>
+      </c>
+      <c r="B76" s="6">
+        <v>30.17</v>
+      </c>
+      <c r="C76" s="6">
+        <v>89.89</v>
+      </c>
+      <c r="D76" s="8">
+        <f t="shared" si="16"/>
+        <v>1.0000000000001563E-2</v>
+      </c>
+      <c r="E76" s="8">
+        <f t="shared" si="17"/>
+        <v>-0.29000000000000625</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3">
+        <v>45795</v>
+      </c>
+      <c r="B77" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C77" s="6">
+        <v>90.42</v>
+      </c>
+      <c r="D77" s="8">
+        <f t="shared" ref="D77:D79" si="18">B77-B76</f>
+        <v>2.9999999999997584E-2</v>
+      </c>
+      <c r="E77" s="8">
+        <f t="shared" ref="E77:E79" si="19">C77-C76</f>
+        <v>0.53000000000000114</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3">
+        <v>45802</v>
+      </c>
+      <c r="B78" s="6">
+        <v>30.2</v>
+      </c>
+      <c r="C78" s="6">
+        <v>90.2</v>
+      </c>
+      <c r="D78" s="8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E78" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.21999999999999886</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3">
+        <v>45809</v>
+      </c>
+      <c r="B79" s="6">
+        <v>30.18</v>
+      </c>
+      <c r="C79" s="6">
+        <v>90.06</v>
+      </c>
+      <c r="D79" s="8">
+        <f t="shared" si="18"/>
+        <v>-1.9999999999999574E-2</v>
+      </c>
+      <c r="E79" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.14000000000000057</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fissures/Fissure_2.xlsx
+++ b/data/Fissures/Fissure_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\PycharmProjects\Fissure-master\data\Fissures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8E6022-DF9F-4C50-AC98-8FE64D67E91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488D1C94-DA97-4DEF-B31E-F0742BBA17BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32070" yWindow="1620" windowWidth="16440" windowHeight="29040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ79"/>
+  <dimension ref="A1:AMJ80"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="3" customWidth="1"/>
@@ -1971,11 +1971,11 @@
         <v>90.42</v>
       </c>
       <c r="D77" s="8">
-        <f t="shared" ref="D77:D79" si="18">B77-B76</f>
+        <f t="shared" ref="D77:D80" si="18">B77-B76</f>
         <v>2.9999999999997584E-2</v>
       </c>
       <c r="E77" s="8">
-        <f t="shared" ref="E77:E79" si="19">C77-C76</f>
+        <f t="shared" ref="E77:E80" si="19">C77-C76</f>
         <v>0.53000000000000114</v>
       </c>
     </row>
@@ -2015,6 +2015,25 @@
       <c r="E79" s="8">
         <f t="shared" si="19"/>
         <v>-0.14000000000000057</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3">
+        <v>45816</v>
+      </c>
+      <c r="B80" s="6">
+        <v>30.18</v>
+      </c>
+      <c r="C80" s="6">
+        <v>90.25</v>
+      </c>
+      <c r="D80" s="8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E80" s="8">
+        <f t="shared" si="19"/>
+        <v>0.18999999999999773</v>
       </c>
     </row>
   </sheetData>
